--- a/data/trans_dic/P12_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P12_1_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces</t>
+          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,26; 18,98</t>
+          <t>12,33; 19,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,6; 21,33</t>
+          <t>13,69; 21,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 13,42</t>
+          <t>7,37; 13,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,04; 15,95</t>
+          <t>10,13; 16,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,16; 23,89</t>
+          <t>15,01; 24,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,18; 22,25</t>
+          <t>13,71; 22,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,32; 15,25</t>
+          <t>8,5; 15,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,64; 19,59</t>
+          <t>13,78; 19,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,4; 19,93</t>
+          <t>14,35; 19,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,54; 20,56</t>
+          <t>14,69; 20,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,82; 13,39</t>
+          <t>8,65; 13,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,27; 16,6</t>
+          <t>12,54; 16,84</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,5; 15,48</t>
+          <t>8,83; 15,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,2; 20,2</t>
+          <t>11,75; 19,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 13,19</t>
+          <t>6,59; 13,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 15,81</t>
+          <t>9,52; 16,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,83; 25,33</t>
+          <t>16,87; 25,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,19; 31,02</t>
+          <t>20,97; 30,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,72; 17,26</t>
+          <t>9,85; 17,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,68; 24,13</t>
+          <t>16,81; 24,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,85; 19,13</t>
+          <t>13,9; 19,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,25; 23,57</t>
+          <t>17,06; 23,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 13,89</t>
+          <t>9,18; 13,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,8; 18,63</t>
+          <t>13,65; 18,71</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,3; 21,94</t>
+          <t>15,15; 21,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,07; 21,34</t>
+          <t>14,8; 21,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,29; 14,83</t>
+          <t>9,19; 14,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 16,41</t>
+          <t>3,79; 16,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,81; 28,54</t>
+          <t>15,49; 28,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,61; 32,17</t>
+          <t>20,38; 31,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,52; 28,12</t>
+          <t>14,37; 28,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,77; 24,79</t>
+          <t>15,79; 25,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,15; 22,05</t>
+          <t>16,28; 22,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,46; 23,15</t>
+          <t>17,57; 23,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 16,41</t>
+          <t>11,52; 16,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,16; 17,59</t>
+          <t>5,2; 17,6</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,05; 22,46</t>
+          <t>17,74; 22,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,6; 18,82</t>
+          <t>14,56; 19,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,32; 15,44</t>
+          <t>11,37; 15,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,92; 15,97</t>
+          <t>11,91; 16,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,29; 26,66</t>
+          <t>20,29; 26,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,74; 29,34</t>
+          <t>22,82; 29,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,48; 19,43</t>
+          <t>14,31; 19,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,69; 66,46</t>
+          <t>18,75; 61,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,28; 22,98</t>
+          <t>19,5; 23,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,62; 22,51</t>
+          <t>18,73; 22,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,04; 16,31</t>
+          <t>13,2; 16,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,96; 49,71</t>
+          <t>15,84; 49,95</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,3; 23,35</t>
+          <t>14,74; 23,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,28; 17,51</t>
+          <t>11,45; 17,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,73; 16,07</t>
+          <t>10,55; 16,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,64; 19,78</t>
+          <t>12,51; 19,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,7; 28,95</t>
+          <t>21,94; 28,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,33; 31,11</t>
+          <t>24,61; 31,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,39; 24,59</t>
+          <t>18,33; 24,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,13; 23,31</t>
+          <t>14,83; 23,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,34; 25,81</t>
+          <t>20,25; 25,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,99; 24,98</t>
+          <t>20,19; 24,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,56; 19,91</t>
+          <t>15,56; 19,89</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,26; 20,8</t>
+          <t>14,94; 20,81</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,9; 11,11</t>
+          <t>4,85; 11,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,49</t>
+          <t>5,03; 11,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,15; 10,02</t>
+          <t>4,16; 10,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,34; 15,61</t>
+          <t>4,3; 15,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,45; 24,2</t>
+          <t>19,45; 24,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,18; 29,65</t>
+          <t>24,34; 29,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,36; 17,72</t>
+          <t>13,08; 17,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,97; 19,63</t>
+          <t>15,1; 19,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,25; 21,07</t>
+          <t>17,08; 20,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21,01; 25,69</t>
+          <t>20,91; 25,69</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,7; 15,63</t>
+          <t>11,84; 15,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,15; 17,37</t>
+          <t>13,17; 17,71</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,65; 18,22</t>
+          <t>15,59; 18,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,47; 17,05</t>
+          <t>14,6; 17,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,58; 12,86</t>
+          <t>10,48; 12,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,02; 14,0</t>
+          <t>9,43; 14,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,94; 23,86</t>
+          <t>21,03; 23,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,41; 27,38</t>
+          <t>24,31; 27,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,16; 17,81</t>
+          <t>15,26; 17,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,46; 38,44</t>
+          <t>18,41; 35,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,76; 20,65</t>
+          <t>18,79; 20,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,82; 21,94</t>
+          <t>19,89; 21,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,38; 15,09</t>
+          <t>13,34; 15,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,22; 27,11</t>
+          <t>15,1; 26,48</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces</t>
+          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>58074; 89917</t>
+          <t>58431; 90336</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>59468; 93251</t>
+          <t>59849; 94146</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31065; 57575</t>
+          <t>31608; 59009</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50730; 80568</t>
+          <t>51199; 81125</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>46478; 73269</t>
+          <t>46032; 73618</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41460; 69961</t>
+          <t>43100; 72146</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28803; 52797</t>
+          <t>29409; 52976</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61015; 87657</t>
+          <t>61664; 86716</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>112382; 155579</t>
+          <t>112029; 154055</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>109289; 154574</t>
+          <t>110385; 155189</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68353; 103780</t>
+          <t>67091; 104604</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>116893; 158126</t>
+          <t>119479; 160434</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31172; 56809</t>
+          <t>32385; 57805</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51091; 84583</t>
+          <t>49194; 82094</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25421; 49739</t>
+          <t>24856; 49806</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42397; 71514</t>
+          <t>43060; 72524</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62595; 94211</t>
+          <t>62726; 94281</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71398; 104523</t>
+          <t>70654; 102344</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36072; 64064</t>
+          <t>36577; 63616</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63806; 92328</t>
+          <t>64318; 91824</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>102357; 141350</t>
+          <t>102729; 144986</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>130407; 178133</t>
+          <t>128918; 176868</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69472; 103962</t>
+          <t>68684; 103615</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>115167; 155482</t>
+          <t>113939; 156184</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82996; 118979</t>
+          <t>82164; 118194</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94505; 133871</t>
+          <t>92858; 132720</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48391; 77213</t>
+          <t>47870; 76679</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22508; 109644</t>
+          <t>25348; 110092</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26533; 47884</t>
+          <t>25988; 48559</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53407; 83355</t>
+          <t>52816; 82709</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24116; 46713</t>
+          <t>23877; 46536</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26234; 41230</t>
+          <t>26271; 42124</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>114702; 156599</t>
+          <t>115599; 156552</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>154782; 205211</t>
+          <t>155698; 204391</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76104; 112713</t>
+          <t>79127; 116165</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43064; 146813</t>
+          <t>43371; 146880</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>223561; 278158</t>
+          <t>219688; 275959</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>169046; 217939</t>
+          <t>168598; 221266</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>130030; 177368</t>
+          <t>130572; 178289</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>123216; 165149</t>
+          <t>123141; 166631</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>144919; 190396</t>
+          <t>144949; 187920</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>173885; 224360</t>
+          <t>174484; 226804</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>119497; 160310</t>
+          <t>118065; 161627</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>182810; 650027</t>
+          <t>183381; 604435</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>376412; 448742</t>
+          <t>380773; 452161</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>358026; 432769</t>
+          <t>360109; 431250</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>257453; 321855</t>
+          <t>260602; 323421</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>321073; 1000266</t>
+          <t>318722; 1004988</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>53649; 81856</t>
+          <t>51686; 82745</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>57601; 89387</t>
+          <t>58476; 90186</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66611; 99739</t>
+          <t>65510; 99962</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60047; 93961</t>
+          <t>59425; 92740</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>123413; 164681</t>
+          <t>124759; 164054</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>185064; 236601</t>
+          <t>187190; 236141</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>135766; 181511</t>
+          <t>135334; 180495</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>127236; 195995</t>
+          <t>124699; 197233</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>187018; 237258</t>
+          <t>186162; 237231</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>254072; 317530</t>
+          <t>256614; 315105</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>211411; 270589</t>
+          <t>211509; 270230</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>200792; 273779</t>
+          <t>196545; 273803</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14626; 33115</t>
+          <t>14461; 33055</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13737; 30668</t>
+          <t>13413; 30858</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11911; 28786</t>
+          <t>11941; 29749</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10443; 37554</t>
+          <t>10342; 36535</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>242841; 302176</t>
+          <t>242910; 301838</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>267496; 328002</t>
+          <t>269259; 329621</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>144075; 191139</t>
+          <t>141086; 190878</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>114013; 149428</t>
+          <t>114934; 149527</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>266864; 325947</t>
+          <t>264293; 323733</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>288494; 352858</t>
+          <t>287186; 352735</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>159830; 213528</t>
+          <t>161684; 214464</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>131733; 173983</t>
+          <t>131926; 177482</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>511718; 595865</t>
+          <t>509923; 596913</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>494723; 582830</t>
+          <t>499231; 586778</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>357852; 435215</t>
+          <t>354602; 433981</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>338161; 472676</t>
+          <t>318314; 475098</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>707484; 806017</t>
+          <t>710527; 806811</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>864606; 969948</t>
+          <t>861070; 968353</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>534327; 627865</t>
+          <t>537946; 631549</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>660423; 1374745</t>
+          <t>658394; 1282747</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1246911; 1373156</t>
+          <t>1249495; 1374408</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1379933; 1527048</t>
+          <t>1384606; 1526110</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>924642; 1042566</t>
+          <t>921440; 1042878</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1058198; 1884525</t>
+          <t>1049894; 1841101</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P12_1_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,33; 19,07</t>
+          <t>12,38; 19,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,69; 21,53</t>
+          <t>13,89; 22,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 13,75</t>
+          <t>7,57; 13,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 16,06</t>
+          <t>10,21; 15,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,01; 24,0</t>
+          <t>14,64; 23,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,71; 22,94</t>
+          <t>12,89; 22,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,5; 15,3</t>
+          <t>8,25; 15,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,78; 19,38</t>
+          <t>13,86; 19,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,35; 19,74</t>
+          <t>14,13; 19,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,69; 20,65</t>
+          <t>14,56; 20,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,65; 13,49</t>
+          <t>8,85; 13,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,54; 16,84</t>
+          <t>12,71; 16,95</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,83; 15,75</t>
+          <t>9,06; 15,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,75; 19,6</t>
+          <t>11,68; 19,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 13,2</t>
+          <t>6,81; 13,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 16,04</t>
+          <t>9,31; 15,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,87; 25,35</t>
+          <t>16,78; 25,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,97; 30,37</t>
+          <t>20,67; 30,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,85; 17,14</t>
+          <t>9,93; 17,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,81; 24,0</t>
+          <t>16,95; 23,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,9; 19,62</t>
+          <t>13,47; 19,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 23,4</t>
+          <t>16,88; 23,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,18; 13,84</t>
+          <t>8,91; 13,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,65; 18,71</t>
+          <t>13,42; 18,13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,15; 21,79</t>
+          <t>15,42; 21,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,8; 21,16</t>
+          <t>14,85; 21,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,19; 14,72</t>
+          <t>9,24; 15,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 16,47</t>
+          <t>11,69; 18,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,49; 28,94</t>
+          <t>16,1; 28,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,38; 31,92</t>
+          <t>20,17; 31,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,37; 28,01</t>
+          <t>14,25; 28,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,79; 25,32</t>
+          <t>15,64; 25,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,28; 22,04</t>
+          <t>16,48; 22,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,57; 23,06</t>
+          <t>17,66; 22,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,52; 16,91</t>
+          <t>11,45; 17,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 17,6</t>
+          <t>13,73; 19,2</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,74; 22,28</t>
+          <t>17,69; 22,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,56; 19,11</t>
+          <t>14,54; 19,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,37; 15,52</t>
+          <t>11,36; 15,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,91; 16,12</t>
+          <t>12,03; 16,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,29; 26,31</t>
+          <t>20,21; 26,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,82; 29,66</t>
+          <t>22,81; 29,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,31; 19,59</t>
+          <t>14,35; 19,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,75; 61,8</t>
+          <t>17,7; 22,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,5; 23,16</t>
+          <t>19,25; 22,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,73; 22,43</t>
+          <t>18,78; 22,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,2; 16,39</t>
+          <t>13,13; 16,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,84; 49,95</t>
+          <t>15,11; 18,28</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,74; 23,6</t>
+          <t>14,96; 23,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,45; 17,66</t>
+          <t>11,27; 17,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,55; 16,1</t>
+          <t>10,56; 16,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,51; 19,52</t>
+          <t>11,55; 17,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,94; 28,84</t>
+          <t>21,52; 29,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,61; 31,05</t>
+          <t>24,3; 30,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,33; 24,45</t>
+          <t>18,42; 24,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,83; 23,45</t>
+          <t>20,52; 25,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,25; 25,81</t>
+          <t>20,4; 25,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,19; 24,79</t>
+          <t>20,0; 24,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,56; 19,89</t>
+          <t>15,56; 19,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,94; 20,81</t>
+          <t>17,61; 21,48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,08</t>
+          <t>4,99; 11,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,03; 11,56</t>
+          <t>4,98; 11,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,16; 10,36</t>
+          <t>4,11; 10,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,3; 15,19</t>
+          <t>4,79; 15,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,45; 24,17</t>
+          <t>19,61; 24,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,34; 29,79</t>
+          <t>24,25; 29,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,08; 17,7</t>
+          <t>13,28; 17,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,1; 19,64</t>
+          <t>14,54; 19,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,08; 20,93</t>
+          <t>17,03; 20,98</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20,91; 25,69</t>
+          <t>20,93; 25,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,84; 15,7</t>
+          <t>11,75; 15,53</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,17; 17,71</t>
+          <t>12,91; 17,02</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,59; 18,25</t>
+          <t>15,71; 18,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,6; 17,16</t>
+          <t>14,49; 17,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,48; 12,83</t>
+          <t>10,62; 12,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,43; 14,08</t>
+          <t>12,18; 14,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,03; 23,88</t>
+          <t>20,81; 23,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,31; 27,34</t>
+          <t>24,31; 27,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,26; 17,91</t>
+          <t>15,3; 17,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,41; 35,86</t>
+          <t>18,31; 20,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,67</t>
+          <t>18,75; 20,73</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,89; 21,92</t>
+          <t>19,89; 21,89</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,34; 15,09</t>
+          <t>13,36; 15,04</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,1; 26,48</t>
+          <t>15,63; 17,36</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65331</t>
+          <t>71072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>73161</t>
+          <t>81987</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>138492</t>
+          <t>153059</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>58431; 90336</t>
+          <t>58633; 92879</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>59849; 94146</t>
+          <t>60737; 96198</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31608; 59009</t>
+          <t>32472; 59931</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51199; 81125</t>
+          <t>56232; 87964</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>46032; 73618</t>
+          <t>44891; 72176</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43100; 72146</t>
+          <t>40546; 69359</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29409; 52976</t>
+          <t>28554; 53575</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61664; 86716</t>
+          <t>67708; 96803</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>112029; 154055</t>
+          <t>110283; 155465</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110385; 155189</t>
+          <t>109433; 153459</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67091; 104604</t>
+          <t>68627; 104736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>119479; 160434</t>
+          <t>132073; 176075</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55944</t>
+          <t>57474</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>77725</t>
+          <t>84490</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>133669</t>
+          <t>141964</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32385; 57805</t>
+          <t>33241; 57555</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49194; 82094</t>
+          <t>48910; 82510</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24856; 49806</t>
+          <t>25673; 50382</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43060; 72524</t>
+          <t>44965; 72752</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62726; 94281</t>
+          <t>62407; 94057</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70654; 102344</t>
+          <t>69667; 103393</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36577; 63616</t>
+          <t>36848; 63986</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64318; 91824</t>
+          <t>71715; 100619</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>102729; 144986</t>
+          <t>99544; 140760</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128918; 176868</t>
+          <t>127588; 176201</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68684; 103615</t>
+          <t>66698; 103961</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>113939; 156184</t>
+          <t>121638; 164303</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65081</t>
+          <t>70129</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33339</t>
+          <t>36986</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98420</t>
+          <t>107115</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82164; 118194</t>
+          <t>83632; 119295</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92858; 132720</t>
+          <t>93170; 132675</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47870; 76679</t>
+          <t>48116; 78479</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25348; 110092</t>
+          <t>55133; 88488</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25988; 48559</t>
+          <t>27013; 48105</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>52816; 82709</t>
+          <t>52277; 82106</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23877; 46536</t>
+          <t>23681; 46676</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26271; 42124</t>
+          <t>29236; 46759</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>115599; 156552</t>
+          <t>117015; 159591</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>155698; 204391</t>
+          <t>156552; 203406</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79127; 116165</t>
+          <t>78626; 116845</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43371; 146880</t>
+          <t>90386; 126446</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143384</t>
+          <t>158388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>356566</t>
+          <t>171713</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>499949</t>
+          <t>330101</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>219688; 275959</t>
+          <t>219025; 275550</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>168598; 221266</t>
+          <t>168350; 222337</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>130572; 178289</t>
+          <t>130530; 174647</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>123141; 166631</t>
+          <t>136091; 182216</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>144949; 187920</t>
+          <t>144333; 189619</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>174484; 226804</t>
+          <t>174390; 225666</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>118065; 161627</t>
+          <t>118382; 159955</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>183381; 604435</t>
+          <t>152431; 191274</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>380773; 452161</t>
+          <t>375798; 448422</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>360109; 431250</t>
+          <t>361110; 430988</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>260602; 323421</t>
+          <t>259192; 324578</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>318722; 1004988</t>
+          <t>300977; 364171</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74503</t>
+          <t>81917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>168554</t>
+          <t>190867</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>243057</t>
+          <t>272784</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>51686; 82745</t>
+          <t>52441; 81895</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>58476; 90186</t>
+          <t>57556; 89908</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>65510; 99962</t>
+          <t>65528; 99876</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59425; 92740</t>
+          <t>65624; 100223</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>124759; 164054</t>
+          <t>122416; 165117</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>187190; 236141</t>
+          <t>184836; 235242</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>135334; 180495</t>
+          <t>135994; 183280</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>124699; 197233</t>
+          <t>170373; 210603</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>186162; 237231</t>
+          <t>187537; 238495</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>256614; 315105</t>
+          <t>254278; 316130</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>211509; 270230</t>
+          <t>211485; 266548</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>196545; 273803</t>
+          <t>246223; 300327</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19849</t>
+          <t>20549</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>130912</t>
+          <t>140656</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>150761</t>
+          <t>161205</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14461; 33055</t>
+          <t>14887; 33116</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13413; 30858</t>
+          <t>13286; 30809</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11941; 29749</t>
+          <t>11806; 30032</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10342; 36535</t>
+          <t>11371; 36855</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>242910; 301838</t>
+          <t>244820; 302012</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>269259; 329621</t>
+          <t>268276; 328913</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>141086; 190878</t>
+          <t>143261; 192444</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>114934; 149527</t>
+          <t>122754; 160702</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>264293; 323733</t>
+          <t>263520; 324490</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>287186; 352735</t>
+          <t>287408; 351599</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>161684; 214464</t>
+          <t>160493; 212175</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>131926; 177482</t>
+          <t>139639; 184069</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>424091</t>
+          <t>459529</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>840257</t>
+          <t>706698</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1264349</t>
+          <t>1166228</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>509923; 596913</t>
+          <t>513815; 599942</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>499231; 586778</t>
+          <t>495485; 585318</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>354602; 433981</t>
+          <t>359407; 432141</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>318314; 475098</t>
+          <t>419022; 502502</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>710527; 806811</t>
+          <t>702932; 799806</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>861070; 968353</t>
+          <t>861161; 969369</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>537946; 631549</t>
+          <t>539349; 630081</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>658394; 1282747</t>
+          <t>665341; 748041</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1249495; 1374408</t>
+          <t>1246315; 1378299</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1384606; 1526110</t>
+          <t>1384715; 1523490</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>921440; 1042878</t>
+          <t>923026; 1039205</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1049894; 1841101</t>
+          <t>1106137; 1228437</t>
         </is>
       </c>
     </row>
